--- a/docs/测试/02-测试用例.xlsx
+++ b/docs/测试/02-测试用例.xlsx
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07 21:19:34</t>
+          <t>2026-10-14 17:45:25</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07 21:19:36</t>
+          <t>2026-10-14 17:45:28</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 id=3a3359b2a3914250ab3943a89f1c5d93</t>
+          <t>HTTP 200 id=141afe77954840dfa70233e0277059ad</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>新密码少于 6 位被拒绝</t>
+          <t>新密码少于 8 位被拒绝</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>code=VR4NJMJXHZ</t>
+          <t>code=SZ7REGN84Q</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>total=7 名称=['历史测试商品', '失败重排商品', '交易测试商品', '排队测试商品', '商品A']</t>
+          <t>total=20 名称=['历史测试商品', '失败重排商品', '交易测试商品', '排队测试商品', '商品A']</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>{"failed_rounds": 1, "buyer_count": 2, "final_result": "SUCCESS", "final_result_label": "交易成功", "last_transaction_at": "2026-10-07 21:19:36"}</t>
+          <t>{"failed_rounds": 1, "buyer_count": 2, "final_result": "SUCCESS", "final_result_label": "交易成功", "last_transaction_at": "2026-10-14 17:45:27"}</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>共 35 条，detail 齐全=True</t>
+          <t>共 85 条，detail 齐全=True</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>total=1 名称=['历史测试商品']</t>
+          <t>total=2 名称=['历史测试商品', '历史测试商品']</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>搜索「_」命中 7 条；不带关键词共 7 条</t>
+          <t>搜索「_」命中 20 条；不带关键词共 20 条</t>
         </is>
       </c>
       <c r="I86" s="9" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 url=/uploads/a7b70ed4799c4a4e8ff48e293652ba32.png</t>
+          <t>HTTP 200 url=/uploads/fb55e3f81e1646cfaaf2be7fcd8b20aa.png</t>
         </is>
       </c>
       <c r="I90" s="8" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>A=50b58378 B=ee5a3c9c</t>
+          <t>A=677e786b B=d7cea909</t>
         </is>
       </c>
       <c r="I104" s="8" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 body=b'{"state":"FROZEN","product":{"id":"7dc672a65b19425a8f6e7aa21'</t>
+          <t>HTTP 200 body=b'{"state":"FROZEN","product":{"id":"29a0422d29774d5985b452aba'</t>
         </is>
       </c>
       <c r="I113" s="8" t="inlineStr">

--- a/docs/测试/02-测试用例.xlsx
+++ b/docs/测试/02-测试用例.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>FR-032、FR-033、FR-035、NFR-006、接口设计§1</t>
+          <t>FR-032、FR-033、FR-034、FR-035、NFR-006、接口设计§1</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>FR-004、FR-005、FR-019、FR-031、NFR-003、NFR-015</t>
+          <t>FR-004、FR-005、FR-006、FR-007、FR-019、FR-031</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>NFR-004、NFR-005</t>
+          <t>NFR-002、NFR-004、NFR-005</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>FR-051</t>
+          <t>FR-051、FR-052</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14 17:45:25</t>
+          <t>2026-10-15 08:42:56</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14 17:45:28</t>
+          <t>2026-10-15 08:42:59</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 id=141afe77954840dfa70233e0277059ad</t>
+          <t>HTTP 200 id=d73dc4e8c0ff4686b2b25317ed52c755</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>不提供注册接口</t>
+          <t>不提供注册接口与退出登录接口</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>FR-033</t>
+          <t>FR-033/FR-034</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>HTTP 404</t>
+          <t>注册接口 404、退出登录接口 404</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>HTTP 404</t>
+          <t>注册 404、退出登录 404</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>FR-013/FR-014</t>
+          <t>FR-013/FR-014/FR-048</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>code=SZ7REGN84Q</t>
+          <t>code=A9W7HKTWM5</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>无效口令码返回 410</t>
+          <t>无效口令码返回 410，且不提供口令码找回接口</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>FR-022/NFR-005</t>
+          <t>FR-022/FR-050/NFR-005</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>HTTP 410 COMMAND_CODE_INVALID</t>
+          <t>查询返回 410；找回接口不存在（404 或 405）</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>HTTP 410 COMMAND_CODE_INVALID</t>
+          <t>查询 410、找回 405</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>total=20 名称=['历史测试商品', '失败重排商品', '交易测试商品', '排队测试商品', '商品A']</t>
+          <t>total=46 名称=['历史测试商品', '失败重排商品', '交易测试商品', '排队测试商品', '商品A']</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>{"failed_rounds": 1, "buyer_count": 2, "final_result": "SUCCESS", "final_result_label": "交易成功", "last_transaction_at": "2026-10-14 17:45:27"}</t>
+          <t>{"failed_rounds": 1, "buyer_count": 2, "final_result": "SUCCESS", "final_result_label": "交易成功", "last_transaction_at": "2026-10-15 08:42:58"}</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>FR-031/NFR-015</t>
+          <t>FR-006/FR-007/FR-031/NFR-015</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>共 85 条，detail 齐全=True</t>
+          <t>共 185 条，detail 齐全=True</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>total=2 名称=['历史测试商品', '历史测试商品']</t>
+          <t>total=4 名称=['历史测试商品', '历史测试商品', '历史测试商品', '历史测试商品']</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>搜索「_」命中 20 条；不带关键词共 20 条</t>
+          <t>搜索「_」命中 46 条；不带关键词共 46 条</t>
         </is>
       </c>
       <c r="I86" s="9" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 url=/uploads/fb55e3f81e1646cfaaf2be7fcd8b20aa.png</t>
+          <t>HTTP 200 url=/uploads/e1ddf7d2f2fb4524813852a27c5cacc6.png</t>
         </is>
       </c>
       <c r="I90" s="8" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>NFR-005</t>
+          <t>NFR-002/NFR-005</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>A=677e786b B=d7cea909</t>
+          <t>A=1c971a9d B=84cd2adb</t>
         </is>
       </c>
       <c r="I104" s="8" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>NFR-005</t>
+          <t>NFR-002/NFR-005</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>12 个前端路由均可访问（SPA 回退正常）</t>
+          <t>12 个前端路由均可访问（含买家端，SPA 回退正常）</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>FR-051</t>
+          <t>FR-051/FR-052</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 body=b'{"state":"FROZEN","product":{"id":"29a0422d29774d5985b452aba'</t>
+          <t>HTTP 200 body=b'{"state":"FROZEN","product":{"id":"69d1d04d5a044ba4a84004d20'</t>
         </is>
       </c>
       <c r="I113" s="8" t="inlineStr">
@@ -6757,13 +6757,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -6787,464 +6788,1828 @@
           <t>覆盖结论</t>
         </is>
       </c>
+      <c r="E1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>FR-000</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>TC-C01、TC-C02、TC-C03、TC-C04、TC-C05、TC-C06、TC-C07、TC-C08、TC-C09、TC-C10、TC-C11、TC-C12、TC-C17、TC-C18、TC-C19、TC-C21、TC-F01、TC-F02、TC-F05、TC-F14、TC-F15、TC-H01、TC-H02</t>
-        </is>
+          <t>FR-001</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>发布商品</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-C01、TC-C03、TC-C04、TC-C05、TC-C06、TC-C07、TC-C08、TC-C09、TC-C10、TC-H01、TC-H02</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（11 条用例）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>FR-001</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>TC-C01、TC-C02、TC-C03、TC-C04、TC-C05、TC-C06、TC-C07、TC-C08、TC-C09、TC-C10、TC-C11、TC-C12、TC-C13、TC-C16、TC-C17、TC-C18、TC-C19、TC-C21、TC-D01、TC-D03、TC-D10、TC-D11、TC-D12、TC-D13、TC-D14、TC-E02、TC-E03、TC-F01、TC-F02、TC-F04、TC-F05、TC-F06、TC-F07、TC-F14、TC-F15、TC-G01、TC-G02、TC-H01、TC-H02</t>
-        </is>
+          <t>FR-002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>商品信息不可修改</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-C21</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FR-002</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>TC-C02、TC-C11、TC-C12、TC-C13、TC-C17、TC-C18、TC-C19、TC-C21、TC-D01、TC-D03、TC-D04、TC-D05、TC-D06、TC-D07、TC-D08、TC-D09、TC-D10、TC-D11、TC-D12、TC-D13、TC-D14、TC-E04、TC-E05、TC-E06、TC-E07、TC-E08、TC-E11、TC-E12、TC-E13、TC-E14、TC-F01、TC-F02、TC-F04、TC-F05、TC-F06、TC-F07、TC-F14、TC-F15、TC-G01、TC-G02</t>
-        </is>
+          <t>FR-003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>下架商品</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-C17、TC-C18、TC-C19</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>FR-003</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>TC-B06、TC-B07、TC-B08、TC-B09、TC-C02、TC-C11、TC-C12、TC-C13、TC-C17、TC-C18、TC-C19、TC-D01、TC-D03、TC-D06、TC-D07、TC-D08、TC-D09、TC-D10、TC-D11、TC-D12、TC-D13、TC-D14、TC-E04、TC-E05、TC-E07、TC-E08、TC-E11、TC-E12、TC-E13、TC-E14、TC-F01、TC-F02、TC-F04、TC-F05、TC-F06、TC-F07、TC-F14、TC-F15、TC-G01、TC-G02</t>
-        </is>
+          <t>FR-004</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>历史商品列表</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-F01、TC-F02、TC-F14、TC-F15</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（4 条用例）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>FR-004</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>TC-A01、TC-A02、TC-A04、TC-B07、TC-B08、TC-B09、TC-C02、TC-C11、TC-C12、TC-C13、TC-D01、TC-D03、TC-D08、TC-D09、TC-E04、TC-E05、TC-E07、TC-E08、TC-E11、TC-E12、TC-E13、TC-E14、TC-F01、TC-F02、TC-F04、TC-F05、TC-F06、TC-F07、TC-F14、TC-F15、TC-G01、TC-G02</t>
-        </is>
+          <t>FR-005</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>历史商品详情</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-F05</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>FR-005</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>TC-A02、TC-A04、TC-B07、TC-B08、TC-B09、TC-C02、TC-C11、TC-C12、TC-C13、TC-D03、TC-D08、TC-E04、TC-E05、TC-E07、TC-E08、TC-E11、TC-E12、TC-E13、TC-E14、TC-F04、TC-F05、TC-F06、TC-F07、TC-G01、TC-G02</t>
-        </is>
+          <t>FR-006</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>历史商品意向购买人</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-F03</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>FR-006</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>TC-A04、TC-C02、TC-C11、TC-C12、TC-C13、TC-D08、TC-E07、TC-E08、TC-E11、TC-E12、TC-E13、TC-E14、TC-F04、TC-F06、TC-F07、TC-G01、TC-G02</t>
-        </is>
+          <t>FR-007</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>商品快照</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-F03</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>FR-007</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>TC-C02、TC-C11、TC-C12、TC-E07、TC-E11、TC-E12、TC-E14、TC-F04、TC-F06、TC-F07、TC-G01、TC-G02</t>
-        </is>
+          <t>FR-008</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>唯一在售</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-C02</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>FR-008</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>TC-C02、TC-C11、TC-C12、TC-E07、TC-E12、TC-E14、TC-F04、TC-F06、TC-G01、TC-G02</t>
-        </is>
+          <t>FR-009</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>手动冻结</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-C11、TC-C12</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>FR-009</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>TC-C11、TC-C12、TC-E07、TC-E14、TC-F04、TC-F06</t>
-        </is>
+          <t>FR-010</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>手动解冻</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-C14、TC-C15、TC-C16</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NFR-000</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>TC-B04、TC-B05、TC-C10、TC-D02、TC-D05、TC-F04、TC-G03、TC-K01、TC-K02、TC-K03、TC-K04、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-011</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>自动冻结</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-C16、TC-E02、TC-E03</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>NFR-001</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>TC-B04、TC-B05、TC-C10、TC-D02、TC-D03、TC-D05、TC-F03、TC-F04、TC-G03、TC-H03、TC-H04、TC-H05、TC-H06、TC-H07、TC-H08、TC-I01、TC-I02、TC-I03、TC-I04、TC-K01、TC-K02、TC-K03、TC-K04、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-012</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>冻结期间不收新意向</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-C13</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NFR-002</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>TC-B04、TC-B05、TC-C10、TC-D02、TC-D03、TC-D05、TC-F03、TC-F04、TC-G03、TC-H03、TC-H04、TC-H05、TC-H06、TC-H07、TC-H08、TC-I01、TC-I02、TC-I03、TC-I04、TC-K01、TC-K02、TC-K03、TC-K04、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-013</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>提交购买意向</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-D01、TC-D10、TC-D11、TC-D12、TC-D13、TC-D14</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（6 条用例）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>NFR-003</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>TC-B04、TC-B05、TC-C10、TC-D02、TC-D03、TC-D05、TC-F03、TC-F04、TC-G03、TC-I01、TC-I02、TC-I03、TC-I04、TC-K01、TC-K02、TC-K03、TC-K04、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-014</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>生成口令码</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-D01</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NFR-004</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>TC-B04、TC-B05、TC-C10、TC-D02、TC-D03、TC-D05、TC-F03、TC-G03、TC-I02、TC-I04、TC-K01、TC-K02、TC-K03、TC-K04、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-015</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>排队</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-D03</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>NFR-005</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>TC-B04、TC-B05、TC-C10、TC-D05、TC-F03、TC-G03、TC-K01、TC-K02、TC-K04、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-016</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>冻结后队列封口</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-C13</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>NFR-006</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>TC-B04、TC-B05、TC-C10、TC-G03、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-017</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>查看意向购买人</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-F07</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>NFR-007</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>TC-C10、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-018</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>导出意向购买人</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-G01、TC-G02</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>NFR-008</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>TC-C10、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-019</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>隐私脱敏</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-F04、TC-F06</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>NFR-009</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>TC-C10、TC-K05、TC-K06、TC-K07、TC-K08</t>
-        </is>
+          <t>FR-020</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>不可手动调整队列</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-I04</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>TBD-03</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>TC-E15</t>
-        </is>
+          <t>FR-021</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>自动递补</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-E01、TC-E07</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>接口设计§1</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>TC-B10、TC-C20、TC-D15、TC-F08、TC-F09、TC-F10、TC-F11</t>
-        </is>
+          <t>FR-022</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>凭口令码查询</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>已覆盖</t>
+          <t>TC-D04、TC-D05、TC-E06</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>接口设计§2</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
+          <t>FR-023</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>凭口令码修改信息</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>TC-D06、TC-D07、TC-E05</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>FR-024</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>凭口令码撤销排队</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>TC-D08、TC-D09</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>FR-025</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>进入交易不可撤销</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>TC-E04、TC-E05</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>FR-026</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>口令码失效</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>TC-D08、TC-E08、TC-E13</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>FR-027</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>交易标记</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>TC-A06</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>已覆盖</t>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>TC-E11</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>FR-028</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>TC-E12</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>FR-029</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>交易失败</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>TC-E07、TC-E14</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>FR-030</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>失败者处理</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>TC-E09、TC-E10、TC-E15、TC-E16、TC-E17、TC-E18</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（6 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>FR-031</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>多次交易记录</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>TC-F03</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>FR-032</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>卖家登录</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>TC-B01、TC-B02、TC-B03</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>FR-033</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>卖家账号不可注册</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>TC-B06</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>FR-034</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>无退出登录</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>TC-B06</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>FR-035</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>修改密码</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>TC-B07、TC-B08、TC-B09</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>FR-036</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>发布商品</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>TC-C01、TC-C03、TC-C04、TC-C05、TC-C06、TC-C07、TC-C08、TC-C09、TC-C10、TC-H01、TC-H02</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>同源需求（同 FR-001），用例见该条</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>FR-037</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>查看历史商品</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>TC-F01、TC-F02、TC-F14、TC-F15</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>同源需求（同 FR-004），用例见该条</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>FR-038</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>查看历史商品详情</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>TC-F05</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>同源需求（同 FR-005），用例见该条</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>FR-039</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>查看意向购买人</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>TC-F07</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>同源需求（同 FR-017），用例见该条</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>FR-040</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>冻结/解冻商品</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>TC-C11、TC-C12、TC-C14、TC-C15、TC-C16</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>同源需求（同 FR-009、FR-010），用例见该条</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>FR-041</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>修改密码</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>TC-B07、TC-B08、TC-B09</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>同源需求（同 FR-035），用例见该条</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>FR-042</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>操作日志</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>TC-F12、TC-F13</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>FR-043</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>匿名浏览</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>TC-A03、TC-A05</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>FR-044</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>无商品在售</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>TC-A01</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>FR-045</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>商品在售</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>TC-A02</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>FR-046</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>商品冻结</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>TC-A04</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>FR-047</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>提交购买意向</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>TC-D01、TC-D10、TC-D11、TC-D12、TC-D13、TC-D14</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>同源需求（同 FR-013），用例见该条</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>FR-048</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>口令码展示</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>TC-D01</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>FR-049</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>凭口令码查询/修改/撤销</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>TC-D04、TC-D05、TC-D06、TC-D07、TC-D08、TC-D09、TC-E05、TC-E06</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>同源需求（同 FR-022、FR-023、FR-024），用例见该条</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>FR-050</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>口令码丢失</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>TC-D05</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>FR-051</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>卖家后台 Web</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>TC-J01、TC-J02、TC-J03、TC-J04、TC-J05</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（5 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>FR-052</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>买家 Web/H5</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>TC-J01</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>FR-053</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Product Backlog</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>过程需求，无功能用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>FR-054</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Sprint Backlog</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>过程需求，无功能用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>FR-055</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Sprint 评审</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>过程需求，无功能用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>FR-056</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Sprint 回顾</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>过程需求，无功能用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>FR-057</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>每日站会</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>过程需求，无功能用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>NFR-001</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>性能：商品详情响应小于 2 秒</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>本轮未纳入（见测试计划「不覆盖范围」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>NFR-002</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>安全：密码哈希存储，HTTPS，防 CSRF、XSS、SQL 注入</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>TC-K01、TC-K04</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>NFR-003</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>隐私：买家姓名、电话仅用于本次交易，交易后脱敏或删除</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>TC-F04</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>NFR-004</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>口令码安全：口令码随机、不可猜测、唯一，不可枚举</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>TC-D02、TC-K03</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（2 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>NFR-005</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>口令码失效：交易成功、交易失败、商品下架或买家撤销后立即失效</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>TC-D05、TC-K01、TC-K02、TC-K04</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（4 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>NFR-006</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>卖家账号安全：固定账号，密码哈希存储，支持修改密码</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>TC-B04、TC-B05、TC-G03</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>NFR-007</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>可用性：系统可用性不低于 99%</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>本轮未纳入（见测试计划「不覆盖范围」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>NFR-008</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>兼容性：支持主流浏览器；移动端适配以最终终端范围为准</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>本轮未纳入（见测试计划「不覆盖范围」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>NFR-009</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>可维护性：模块化、接口文档、日志规范</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>TC-C10、TC-K05、TC-K06、TC-K07、TC-K08</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（5 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>NFR-010</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>审计：卖家关键操作可追溯，历史交易过程完整保留</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>TC-F13</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>NFR-011</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>备份：数据库定期备份，可恢复</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>本轮未纳入（见测试计划「不覆盖范围」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>NFR-012</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>图片：限制格式（仅支持JPG/PNG）、大小（单张≤5MB），防止恶意上传；最多一张主图</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>TC-H03、TC-H04、TC-H05、TC-H06、TC-H07、TC-H08</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（6 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>NFR-013</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>并发：商品冻结、排队、递补需保证顺序一致性，防止超卖</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>TC-I01、TC-I02、TC-I03</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>NFR-014</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>先到先得：队列顺序严格按提交时间，不可人为干预</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>TC-D03、TC-I02、TC-I04</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（3 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>NFR-015</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>历史完整性：同一商品多次交易记录必须完整保留，不可只存最终结果</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>TC-F03</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>TBD-03</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>（接口文档章节）</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>TC-E15</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖（1 条用例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n"/>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>统计</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>需求总数 72 条</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>已覆盖 63 条</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>本轮应覆盖 63 条</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>覆盖率 100.0%（同源需求计入；过程需求 5 条、本轮未纳入 4 条不计入）</t>
         </is>
       </c>
     </row>

--- a/docs/测试/02-测试用例.xlsx
+++ b/docs/测试/02-测试用例.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="执行环境与说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'测试用例明细'!$A$1:$K$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'测试用例明细'!$A$1:$K$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -947,14 +947,14 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>性能</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
@@ -964,139 +964,166 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
+          <t>NFR-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
           <t>FR-051、FR-052</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>全部模块</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="E20" s="5" t="n">
+      <c r="C21" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="F21" s="5" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>执行信息</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>用例总数</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>113</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>用例总数</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>通过率</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>98.2%</t>
-        </is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>开始时间</t>
+          <t>通过率</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 08:42:56</t>
+          <t>98.3%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>结束时间</t>
+          <t>开始时间</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 08:42:59</t>
+          <t>2026-10-15 08:46:46</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>后端地址</t>
+          <t>结束时间</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:8000</t>
+          <t>2026-10-15 08:46:49</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>前端地址</t>
+          <t>后端地址</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>http://127.0.0.1:5173</t>
+          <t>http://127.0.0.1:8000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
+          <t>前端地址</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:5173</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
           <t>缺陷总数</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B32" s="7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1111,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1320,7 +1347,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 id=d73dc4e8c0ff4686b2b25317ed52c755</t>
+          <t>HTTP 200 id=6ac46c255818442eaec170269b1c7763</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -3092,7 +3119,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>code=A9W7HKTWM5</t>
+          <t>code=9968Y323QJ</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
@@ -4660,7 +4687,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>total=46 名称=['历史测试商品', '失败重排商品', '交易测试商品', '排队测试商品', '商品A']</t>
+          <t>total=101 名称=['历史测试商品', '失败重排商品', '交易测试商品', '排队测试商品', '商品A']</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -4709,7 +4736,7 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>{"failed_rounds": 1, "buyer_count": 2, "final_result": "SUCCESS", "final_result_label": "交易成功", "last_transaction_at": "2026-10-15 08:42:58"}</t>
+          <t>{"failed_rounds": 1, "buyer_count": 2, "final_result": "SUCCESS", "final_result_label": "交易成功", "last_transaction_at": "2026-10-15 08:46:48"}</t>
         </is>
       </c>
       <c r="I73" s="8" t="inlineStr">
@@ -5248,7 +5275,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>共 185 条，detail 齐全=True</t>
+          <t>共 391 条，detail 齐全=True</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
@@ -5297,7 +5324,7 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>total=4 名称=['历史测试商品', '历史测试商品', '历史测试商品', '历史测试商品']</t>
+          <t>total=8 名称=['历史测试商品', '历史测试商品', '历史测试商品', '历史测试商品', '历史测试商品', '历史测试商品', '历史测试商品', '历史测试商品']</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
@@ -5346,7 +5373,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>搜索「_」命中 46 条；不带关键词共 46 条</t>
+          <t>搜索「_」命中 101 条；不带关键词共 101 条</t>
         </is>
       </c>
       <c r="I86" s="9" t="inlineStr">
@@ -5550,7 +5577,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 url=/uploads/e1ddf7d2f2fb4524813852a27c5cacc6.png</t>
+          <t>HTTP 200 url=/uploads/d0b30d4d4001407c814116e09ceddb28.png</t>
         </is>
       </c>
       <c r="I90" s="8" t="inlineStr">
@@ -6240,7 +6267,7 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>A=1c971a9d B=84cd2adb</t>
+          <t>A=93d180e1 B=9a5f1e4b</t>
         </is>
       </c>
       <c r="I104" s="8" t="inlineStr">
@@ -6503,42 +6530,42 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>TC-J01</t>
+          <t>TC-L01</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>性能</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>12 个前端路由均可访问（含买家端，SPA 回退正常）</t>
+          <t>商品详情接口响应时间小于 2 秒</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>FR-051/FR-052</t>
+          <t>NFR-001</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>后端 127.0.0.1:8000 与前端 Vite 开发服务器 127.0.0.1:5173 均已启动</t>
+          <t>后端服务已启动</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>1) 以 HTTP GET 访问前端路由或模块资源，依次访问 12 个前端路由；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
+          <t>调用被测接口，按用例标题所述场景构造请求</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>全部返回 200 且包含挂载点 #app</t>
+          <t>各次响应耗时均小于 2000 ms</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>异常路由: 无</t>
+          <t>平均 7.0 ms，最慢 23.2 ms（5 次采样）</t>
         </is>
       </c>
       <c r="I110" s="8" t="inlineStr">
@@ -6552,42 +6579,42 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>TC-J02</t>
+          <t>TC-L02</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>性能</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Vite 开发服务器正常编译入口模块</t>
+          <t>在售商品状态接口响应时间小于 2 秒</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>FR-051</t>
+          <t>NFR-001</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>后端 127.0.0.1:8000 与前端 Vite 开发服务器 127.0.0.1:5173 均已启动</t>
+          <t>后端服务已启动</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>1) 以 HTTP GET 访问前端路由或模块资源，GET /src/main.js；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
+          <t>调用被测接口，按用例标题所述场景构造请求</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 且 Content-Type 为 JavaScript</t>
+          <t>各次响应耗时均小于 2000 ms</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 CT=text/javascript</t>
+          <t>平均 7.4 ms，最慢 25.4 ms（5 次采样）</t>
         </is>
       </c>
       <c r="I111" s="8" t="inlineStr">
@@ -6601,42 +6628,42 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>TC-J03</t>
+          <t>TC-L03</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>性能</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Vue 单文件组件被正常编译</t>
+          <t>卖家后台列表接口响应时间小于 2 秒</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>FR-051</t>
+          <t>NFR-001</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>后端 127.0.0.1:8000 与前端 Vite 开发服务器 127.0.0.1:5173 均已启动</t>
+          <t>后端服务已启动</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>1) 以 HTTP GET 访问前端路由或模块资源，GET /src/App.vue；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
+          <t>调用被测接口，按用例标题所述场景构造请求</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>各次响应耗时均小于 2000 ms</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>平均 9.1 ms，最慢 29.9 ms（9 次采样）（历史 / 意向 / 日志，每项 3 次）</t>
         </is>
       </c>
       <c r="I112" s="8" t="inlineStr">
@@ -6650,42 +6677,42 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>TC-J04</t>
+          <t>TC-L04</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>性能</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Vite 代理 /api 到后端成功（前后端联调打通）</t>
+          <t>凭口令码查询接口响应时间小于 2 秒</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>FR-051</t>
+          <t>NFR-001</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>后端 127.0.0.1:8000 与前端 Vite 开发服务器 127.0.0.1:5173 均已启动</t>
+          <t>后端服务已启动</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>1) 以 HTTP GET 访问前端路由或模块资源，GET /api/products/current（经 Vite 代理）；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
+          <t>调用被测接口，按用例标题所述场景构造请求</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 且返回后端 JSON（含 state 字段）</t>
+          <t>各次响应耗时均小于 2000 ms</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 body=b'{"state":"FROZEN","product":{"id":"69d1d04d5a044ba4a84004d20'</t>
+          <t>平均 13.9 ms，最慢 24.5 ms（5 次采样）（口令码 JW4V83ZB5N）</t>
         </is>
       </c>
       <c r="I113" s="8" t="inlineStr">
@@ -6699,7 +6726,7 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>TC-J05</t>
+          <t>TC-J01</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -6709,12 +6736,12 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>卖家发布页组件可编译</t>
+          <t>12 个前端路由均可访问（含买家端，SPA 回退正常）</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>FR-051</t>
+          <t>FR-051/FR-052</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -6724,17 +6751,17 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>1) 以 HTTP GET 访问前端路由或模块资源，GET /src/views/seller/PublishView.vue；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
+          <t>1) 以 HTTP GET 访问前端路由或模块资源，依次访问 12 个前端路由；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>全部返回 200 且包含挂载点 #app</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200</t>
+          <t>异常路由: 无</t>
         </is>
       </c>
       <c r="I114" s="8" t="inlineStr">
@@ -6745,8 +6772,204 @@
       <c r="J114" s="4" t="inlineStr"/>
       <c r="K114" s="4" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>TC-J02</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Vite 开发服务器正常编译入口模块</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>FR-051</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>后端 127.0.0.1:8000 与前端 Vite 开发服务器 127.0.0.1:5173 均已启动</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>1) 以 HTTP GET 访问前端路由或模块资源，GET /src/main.js；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 且 Content-Type 为 JavaScript</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 CT=text/javascript</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr"/>
+      <c r="K115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>TC-J03</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Vue 单文件组件被正常编译</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>FR-051</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>后端 127.0.0.1:8000 与前端 Vite 开发服务器 127.0.0.1:5173 均已启动</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>1) 以 HTTP GET 访问前端路由或模块资源，GET /src/App.vue；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr"/>
+      <c r="K116" s="4" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>TC-J04</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Vite 代理 /api 到后端成功（前后端联调打通）</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>FR-051</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>后端 127.0.0.1:8000 与前端 Vite 开发服务器 127.0.0.1:5173 均已启动</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>1) 以 HTTP GET 访问前端路由或模块资源，GET /api/products/current（经 Vite 代理）；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 且返回后端 JSON（含 state 字段）</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 body=b'{"state":"ON_SALE","product":{"id":"c28f5f00d0244ca1b07bbe81'</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>TC-J05</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>卖家发布页组件可编译</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>FR-051</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>后端 127.0.0.1:8000 与前端 Vite 开发服务器 127.0.0.1:5173 均已启动</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>1) 以 HTTP GET 访问前端路由或模块资源，GET /src/views/seller/PublishView.vue；2) 校验 HTTP 200、SPA 挂载点与代理连通性</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200</t>
+        </is>
+      </c>
+      <c r="I118" s="8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr"/>
+      <c r="K118" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K114"/>
+  <autoFilter ref="A1:K118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8207,12 +8430,16 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>TC-L01、TC-L02、TC-L03、TC-L04</t>
+        </is>
+      </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>本轮未纳入（见测试计划「不覆盖范围」）</t>
+          <t>已覆盖（4 条用例）</t>
         </is>
       </c>
     </row>
@@ -8599,17 +8826,17 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>已覆盖 63 条</t>
+          <t>已覆盖 64 条</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>本轮应覆盖 63 条</t>
+          <t>本轮应覆盖 64 条</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>覆盖率 100.0%（同源需求计入；过程需求 5 条、本轮未纳入 4 条不计入）</t>
+          <t>覆盖率 100.0%（同源需求计入；过程需求 5 条、本轮未纳入 3 条不计入）</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8985,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
@@ -8769,7 +8996,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>111 / 2</t>
+          <t>115 / 2</t>
         </is>
       </c>
     </row>
@@ -8781,7 +9008,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.3%</t>
         </is>
       </c>
     </row>
